--- a/outputs/2026-08-20-development-plan/IconGen-前后端详细开发计划.xlsx
+++ b/outputs/2026-08-20-development-plan/IconGen-前后端详细开发计划.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阶段概览" sheetId="1" r:id="R666cb2548f71404d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前端开发计划" sheetId="2" r:id="R0cd38a0d05c34783"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后端开发计划" sheetId="3" r:id="R80f6164390fb4dba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阶段概览" sheetId="1" r:id="R965afc9559d74b34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前端开发计划" sheetId="2" r:id="R259bc82ba8724d77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后端开发计划" sheetId="3" r:id="R65e4e925a7984558"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -145,7 +145,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -155,7 +155,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -166,7 +166,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -176,7 +176,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -9188,7 +9188,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3042b63f7ccf4652"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd32269f4f5cd4828"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20068,7 +20068,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57ea623ab2b84c0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86bbe861315b4c79"/>
   </x:tableParts>
 </x:worksheet>
 </file>